--- a/maintenance_forms/023_fire_safety_equipment_maintenance_report--maintenance_forms.xlsx
+++ b/maintenance_forms/023_fire_safety_equipment_maintenance_report--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'inspection'}</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Inspection'}</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'working'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Working'}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'broken'}</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Broken'}</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_team'}</t>
+          <t>facility_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility Team'}</t>
+          <t>Facility Team</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'external_contractor'}</t>
+          <t>external_contractor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'External Contractor'}</t>
+          <t>External Contractor</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_team'}</t>
+          <t>facility_team</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility Team'}</t>
+          <t>Facility Team</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'external_contractor'}</t>
+          <t>external_contractor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'External Contractor'}</t>
+          <t>External Contractor</t>
         </is>
       </c>
     </row>
